--- a/sample/Master_Input_DEMO.xlsx
+++ b/sample/Master_Input_DEMO.xlsx
@@ -884,7 +884,6 @@
       <c r="B3" s="74" t="n"/>
       <c r="C3" s="75" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5" ht="26.1" customHeight="1" s="29">
       <c r="A5" s="28" t="inlineStr">
         <is>
@@ -899,7 +898,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="26.1" customHeight="1" s="29">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -945,7 +943,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="26.1" customHeight="1" s="29">
       <c r="A14" s="28" t="inlineStr">
         <is>
@@ -1070,7 +1067,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25" ht="26.1" customHeight="1" s="29">
       <c r="A25" s="28" t="inlineStr">
         <is>
@@ -1316,7 +1312,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="26.1" customHeight="1" s="29">
       <c r="A41" s="28" t="inlineStr">
         <is>
@@ -1596,7 +1591,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66" ht="26.1" customHeight="1" s="29">
       <c r="A66" s="28" t="inlineStr">
         <is>
@@ -1707,7 +1701,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77" ht="26.1" customHeight="1" s="29">
       <c r="A77" s="28" t="inlineStr">
         <is>
@@ -1775,7 +1768,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84" ht="26.1" customHeight="1" s="29">
       <c r="A84" s="28" t="inlineStr">
         <is>
@@ -1835,7 +1827,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90" ht="26.1" customHeight="1" s="29">
       <c r="A90" s="28" t="inlineStr">
         <is>
@@ -1962,7 +1953,6 @@
         </is>
       </c>
     </row>
-    <row r="98"/>
     <row r="99" ht="26.1" customHeight="1" s="29">
       <c r="A99" s="28" t="inlineStr">
         <is>
@@ -2088,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -2111,7 +2101,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="38.1" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -2149,28 +2138,6 @@
       <c r="B8" s="72" t="n"/>
       <c r="C8" s="72" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -2186,7 +2153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -2210,7 +2177,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="38.1" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -2248,28 +2214,6 @@
       <c r="B8" s="72" t="n"/>
       <c r="C8" s="72" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -2285,7 +2229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -2309,7 +2253,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -2347,28 +2290,6 @@
       <c r="B8" s="72" t="n"/>
       <c r="C8" s="72" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -2384,7 +2305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -2406,7 +2327,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="38.1" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -2435,28 +2355,6 @@
       <c r="A8" s="72" t="n"/>
       <c r="B8" s="72" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
@@ -2472,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -2494,7 +2392,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="38.1" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -2523,28 +2420,6 @@
       <c r="A8" s="72" t="n"/>
       <c r="B8" s="72" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
@@ -3204,7 +3079,11 @@
           <t>Authorized Capital Description *</t>
         </is>
       </c>
-      <c r="C49" s="69" t="n"/>
+      <c r="C49" s="69" t="inlineStr">
+        <is>
+          <t>Rs. 10,00,000/- (Rupees Ten Lakh divided into 1,00,000 Equity Shares of Rs. 10/- each)</t>
+        </is>
+      </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
           <t>AUTO-GENERATED from the numbers above when you run Generate Final Set. Leave blank to auto-fill. Type your own sentence here to override (auto-fill is then skipped — clear the cell to re-enable).</t>
@@ -3301,7 +3180,11 @@
           <t>Issued Capital Description *</t>
         </is>
       </c>
-      <c r="C56" s="69" t="n"/>
+      <c r="C56" s="69" t="inlineStr">
+        <is>
+          <t>Rs. 1,00,000/- (Rupees One Lakh divided into 10,000 Equity Shares of Rs. 10/- each)</t>
+        </is>
+      </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
           <t>AUTO-GENERATED from the numbers above when you run Generate Final Set. Leave blank to auto-fill. Type your own sentence here to override (auto-fill is then skipped — clear the cell to re-enable).</t>
@@ -3398,7 +3281,11 @@
           <t>Subscribed and Paid-up Capital *</t>
         </is>
       </c>
-      <c r="C63" s="69" t="n"/>
+      <c r="C63" s="69" t="inlineStr">
+        <is>
+          <t>Rs. 1,00,000/- (Rupees One Lakh divided into 10,000 Equity Shares of Rs. 10/- each)</t>
+        </is>
+      </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
           <t>AUTO-GENERATED from the numbers above when you run Generate Final Set. Leave blank to auto-fill. Type your own sentence here to override (auto-fill is then skipped — clear the cell to re-enable).</t>
@@ -3559,7 +3446,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -3843,7 +3729,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="36" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -4255,7 +4140,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -4515,7 +4399,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32.1" customHeight="1" s="29">
       <c r="B4" s="24" t="inlineStr">
         <is>
@@ -4648,7 +4531,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="29">
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -4660,7 +4542,6 @@
           <t>Nil</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Use 'Nil' if none, else amount.</t>
@@ -4678,7 +4559,6 @@
           <t>Nil</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" s="22" t="inlineStr">
         <is>
           <t>Use 'Nil' if none, else amount.</t>
@@ -4726,7 +4606,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="27.95" customHeight="1" s="29">
       <c r="B4" s="24" t="inlineStr">
         <is>
@@ -5168,7 +5047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -5214,7 +5093,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="38.1" customHeight="1" s="29">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -5383,26 +5261,6 @@
       <c r="M10" s="72" t="n"/>
       <c r="N10" s="66" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
@@ -5448,7 +5306,6 @@
       <c r="C1" s="74" t="n"/>
       <c r="D1" s="75" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3" ht="32.1" customHeight="1" s="29">
       <c r="B3" s="11" t="inlineStr">
         <is>
